--- a/inst/grading_formats.xlsx
+++ b/inst/grading_formats.xlsx
@@ -1,53 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dataquieR development\QualityIndicatorFunctions\QualityIndicatorFunctions\inst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/struckmanns/git/gitlab/QualityIndicatorFunctions/QualityIndicatorFunctions/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5198B844-9839-6C4D-84F9-576A9375BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="38400" windowHeight="21096"/>
+    <workbookView xWindow="4680" yWindow="600" windowWidth="33720" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dqindicators" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>33 102 172</t>
-  </si>
-  <si>
-    <t>67 147 195</t>
-  </si>
-  <si>
-    <t>227 186 20</t>
-  </si>
-  <si>
-    <t>214 96 77</t>
-  </si>
-  <si>
-    <t>178 23 43</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -70,13 +44,28 @@
   </si>
   <si>
     <t xml:space="preserve">Critical  </t>
+  </si>
+  <si>
+    <t>227 242 253</t>
+  </si>
+  <si>
+    <t>207 232 243</t>
+  </si>
+  <si>
+    <t>244 199 195</t>
+  </si>
+  <si>
+    <t>229 115 104</t>
+  </si>
+  <si>
+    <t>196 60 57</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -112,7 +101,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -389,78 +378,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
